--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\Mexico EPS\InputData\elec\BPMCCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EB433C41-A8D6-45E3-B973-F657D5AF33FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2031F0C3-A086-4546-8905-732AAB6A005E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29760" yWindow="960" windowWidth="18120" windowHeight="13665" activeTab="2" xr2:uid="{7D95EDE5-FBCC-4BA7-83B7-76A2D6E6B9C3}"/>
+    <workbookView xWindow="47655" yWindow="885" windowWidth="18630" windowHeight="13710" activeTab="2" xr2:uid="{7D95EDE5-FBCC-4BA7-83B7-76A2D6E6B9C3}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="93">
   <si>
     <t>BPMCCS BAU Policy Mandated Capacity Construction Schedule</t>
   </si>
@@ -287,25 +287,49 @@
     <t>2026 - onward</t>
   </si>
   <si>
-    <t>https://app.cfe.mx/Aplicaciones/OTROS/Boletines/boletin?i=6049&amp;utm_</t>
-  </si>
-  <si>
     <t>Capacity additions (MW)</t>
-  </si>
-  <si>
-    <t>MW solar 2024</t>
-  </si>
-  <si>
-    <t>https://www.power-technology.com/data-insights/power-plant-profile-tastiota-solar-pv-park-mexico/</t>
-  </si>
-  <si>
-    <t>MW solar 2024 (converted to ac power)</t>
   </si>
   <si>
     <t>MW solar 2026 onward</t>
   </si>
   <si>
     <t>MW wind 2026 onward</t>
+  </si>
+  <si>
+    <t>MW solar (2024)</t>
+  </si>
+  <si>
+    <t>https://mexicobusiness.news/energy/news/mexicos-solar-growth-strong-policy-grid-gaps-loom?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>https://www.naturalgasintel.com/news/villa-de-reyes-adds-450-mw-of-natural-gas-capacity-to-mexicos-power-grid/?utm_source=chatgpt.com</t>
+  </si>
+  <si>
+    <t>MW Gas CC 2024</t>
+  </si>
+  <si>
+    <t>MW Gas CC 2026</t>
+  </si>
+  <si>
+    <t>MW Gas CC 2027</t>
+  </si>
+  <si>
+    <t>https://naturalgasintel.com/news/mexicos-cfe-adds-14-gw-of-natural-gas-generation-as-demand-rises/#:~:text=In%20a%20mixed%20development%20scheme,recent%20years%2C%E2%80%9D%20management%20said.</t>
+  </si>
+  <si>
+    <t>MW Gas CC 2025</t>
+  </si>
+  <si>
+    <t>https://wwindea.org/GlobalStatistics</t>
+  </si>
+  <si>
+    <t>MW wind 2024</t>
+  </si>
+  <si>
+    <t>MW wind 2025</t>
+  </si>
+  <si>
+    <t>https://www.mordorintelligence.com/industry-reports/mexico-wind-energy-market</t>
   </si>
 </sst>
 </file>
@@ -957,7 +981,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DA530D8-EFD0-462C-92DC-731722C899CD}">
-  <dimension ref="A1:O152"/>
+  <dimension ref="A1:S152"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.44140625" customWidth="1"/>
@@ -3015,47 +3039,47 @@
         <v>33</v>
       </c>
     </row>
-    <row r="65" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>2012</v>
       </c>
@@ -3098,8 +3122,20 @@
       <c r="O74">
         <v>2025</v>
       </c>
-    </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="P74">
+        <v>2026</v>
+      </c>
+      <c r="Q74">
+        <v>2027</v>
+      </c>
+      <c r="R74">
+        <v>2028</v>
+      </c>
+      <c r="S74">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>17</v>
       </c>
@@ -3139,8 +3175,32 @@
       <c r="M75">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N75">
+        <f>'2024 onward additions'!B2</f>
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <f>'2024 onward additions'!C2</f>
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <f>'2024 onward additions'!D2</f>
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <f>'2024 onward additions'!E2</f>
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <f>'2024 onward additions'!F2</f>
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <f>'2024 onward additions'!G2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -3180,8 +3240,32 @@
       <c r="M76">
         <v>4.5</v>
       </c>
-    </row>
-    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N76">
+        <f>'2024 onward additions'!B3</f>
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <f>'2024 onward additions'!C3</f>
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <f>'2024 onward additions'!D3</f>
+        <v>0</v>
+      </c>
+      <c r="Q76">
+        <f>'2024 onward additions'!E3</f>
+        <v>0</v>
+      </c>
+      <c r="R76">
+        <f>'2024 onward additions'!F3</f>
+        <v>0</v>
+      </c>
+      <c r="S76">
+        <f>'2024 onward additions'!G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>19</v>
       </c>
@@ -3221,8 +3305,32 @@
       <c r="M77">
         <v>765</v>
       </c>
-    </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N77">
+        <f>'2024 onward additions'!B4</f>
+        <v>1778</v>
+      </c>
+      <c r="O77">
+        <f>'2024 onward additions'!C4</f>
+        <v>1436</v>
+      </c>
+      <c r="P77">
+        <f>'2024 onward additions'!D4</f>
+        <v>1537</v>
+      </c>
+      <c r="Q77">
+        <f>'2024 onward additions'!E4</f>
+        <v>1000</v>
+      </c>
+      <c r="R77">
+        <f>'2024 onward additions'!F4</f>
+        <v>0</v>
+      </c>
+      <c r="S77">
+        <f>'2024 onward additions'!G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>20</v>
       </c>
@@ -3262,8 +3370,32 @@
       <c r="M78">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N78">
+        <f>'2024 onward additions'!B5</f>
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <f>'2024 onward additions'!C5</f>
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <f>'2024 onward additions'!D5</f>
+        <v>0</v>
+      </c>
+      <c r="Q78">
+        <f>'2024 onward additions'!E5</f>
+        <v>0</v>
+      </c>
+      <c r="R78">
+        <f>'2024 onward additions'!F5</f>
+        <v>0</v>
+      </c>
+      <c r="S78">
+        <f>'2024 onward additions'!G5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>21</v>
       </c>
@@ -3303,8 +3435,32 @@
       <c r="M79">
         <v>0</v>
       </c>
-    </row>
-    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="N79">
+        <f>'2024 onward additions'!B6</f>
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <f>'2024 onward additions'!C6</f>
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <f>'2024 onward additions'!D6</f>
+        <v>0</v>
+      </c>
+      <c r="Q79">
+        <f>'2024 onward additions'!E6</f>
+        <v>0</v>
+      </c>
+      <c r="R79">
+        <f>'2024 onward additions'!F6</f>
+        <v>0</v>
+      </c>
+      <c r="S79">
+        <f>'2024 onward additions'!G6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>22</v>
       </c>
@@ -3344,8 +3500,32 @@
       <c r="M80">
         <v>134</v>
       </c>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N80">
+        <f>'2024 onward additions'!B7</f>
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <f>'2024 onward additions'!C7</f>
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <f>'2024 onward additions'!D7</f>
+        <v>0</v>
+      </c>
+      <c r="Q80">
+        <f>'2024 onward additions'!E7</f>
+        <v>0</v>
+      </c>
+      <c r="R80">
+        <f>'2024 onward additions'!F7</f>
+        <v>0</v>
+      </c>
+      <c r="S80">
+        <f>'2024 onward additions'!G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>23</v>
       </c>
@@ -3385,8 +3565,32 @@
       <c r="M81">
         <v>934</v>
       </c>
-    </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N81">
+        <f>'2024 onward additions'!B8</f>
+        <v>1600</v>
+      </c>
+      <c r="O81">
+        <f>'2024 onward additions'!C8</f>
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <f>'2024 onward additions'!D8</f>
+        <v>0</v>
+      </c>
+      <c r="Q81">
+        <f>'2024 onward additions'!E8</f>
+        <v>469.49</v>
+      </c>
+      <c r="R81">
+        <f>'2024 onward additions'!F8</f>
+        <v>1927.38</v>
+      </c>
+      <c r="S81">
+        <f>'2024 onward additions'!G8</f>
+        <v>74.13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>24</v>
       </c>
@@ -3426,8 +3630,32 @@
       <c r="M82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N82">
+        <f>'2024 onward additions'!B9</f>
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <f>'2024 onward additions'!C9</f>
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <f>'2024 onward additions'!D9</f>
+        <v>0</v>
+      </c>
+      <c r="Q82">
+        <f>'2024 onward additions'!E9</f>
+        <v>0</v>
+      </c>
+      <c r="R82">
+        <f>'2024 onward additions'!F9</f>
+        <v>0</v>
+      </c>
+      <c r="S82">
+        <f>'2024 onward additions'!G9</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>25</v>
       </c>
@@ -3467,8 +3695,32 @@
       <c r="M83">
         <v>2.8779999999999291</v>
       </c>
-    </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N83">
+        <f>'2024 onward additions'!B10</f>
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <f>'2024 onward additions'!C10</f>
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <f>'2024 onward additions'!D10</f>
+        <v>0</v>
+      </c>
+      <c r="Q83">
+        <f>'2024 onward additions'!E10</f>
+        <v>0</v>
+      </c>
+      <c r="R83">
+        <f>'2024 onward additions'!F10</f>
+        <v>0</v>
+      </c>
+      <c r="S83">
+        <f>'2024 onward additions'!G10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>26</v>
       </c>
@@ -3508,8 +3760,32 @@
       <c r="M84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N84">
+        <f>'2024 onward additions'!B11</f>
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <f>'2024 onward additions'!C11</f>
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <f>'2024 onward additions'!D11</f>
+        <v>0</v>
+      </c>
+      <c r="Q84">
+        <f>'2024 onward additions'!E11</f>
+        <v>0</v>
+      </c>
+      <c r="R84">
+        <f>'2024 onward additions'!F11</f>
+        <v>0</v>
+      </c>
+      <c r="S84">
+        <f>'2024 onward additions'!G11</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>27</v>
       </c>
@@ -3549,8 +3825,32 @@
       <c r="M85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N85">
+        <f>'2024 onward additions'!B12</f>
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <f>'2024 onward additions'!C12</f>
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <f>'2024 onward additions'!D12</f>
+        <v>0</v>
+      </c>
+      <c r="Q85">
+        <f>'2024 onward additions'!E12</f>
+        <v>0</v>
+      </c>
+      <c r="R85">
+        <f>'2024 onward additions'!F12</f>
+        <v>0</v>
+      </c>
+      <c r="S85">
+        <f>'2024 onward additions'!G12</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>28</v>
       </c>
@@ -3590,8 +3890,32 @@
       <c r="M86">
         <v>80</v>
       </c>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N86">
+        <f>'2024 onward additions'!B13</f>
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <f>'2024 onward additions'!C13</f>
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <f>'2024 onward additions'!D13</f>
+        <v>0</v>
+      </c>
+      <c r="Q86">
+        <f>'2024 onward additions'!E13</f>
+        <v>0</v>
+      </c>
+      <c r="R86">
+        <f>'2024 onward additions'!F13</f>
+        <v>0</v>
+      </c>
+      <c r="S86">
+        <f>'2024 onward additions'!G13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>29</v>
       </c>
@@ -3631,8 +3955,32 @@
       <c r="M87">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N87">
+        <f>'2024 onward additions'!B14</f>
+        <v>0</v>
+      </c>
+      <c r="O87">
+        <f>'2024 onward additions'!C14</f>
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <f>'2024 onward additions'!D14</f>
+        <v>0</v>
+      </c>
+      <c r="Q87">
+        <f>'2024 onward additions'!E14</f>
+        <v>0</v>
+      </c>
+      <c r="R87">
+        <f>'2024 onward additions'!F14</f>
+        <v>0</v>
+      </c>
+      <c r="S87">
+        <f>'2024 onward additions'!G14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>30</v>
       </c>
@@ -3672,8 +4020,32 @@
       <c r="M88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N88">
+        <f>'2024 onward additions'!B15</f>
+        <v>360</v>
+      </c>
+      <c r="O88">
+        <f>'2024 onward additions'!C15</f>
+        <v>120</v>
+      </c>
+      <c r="P88">
+        <f>'2024 onward additions'!D15</f>
+        <v>0</v>
+      </c>
+      <c r="Q88">
+        <f>'2024 onward additions'!E15</f>
+        <v>170.05</v>
+      </c>
+      <c r="R88">
+        <f>'2024 onward additions'!F15</f>
+        <v>698.1</v>
+      </c>
+      <c r="S88">
+        <f>'2024 onward additions'!G15</f>
+        <v>26.849999999999998</v>
+      </c>
+    </row>
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>31</v>
       </c>
@@ -3713,8 +4085,32 @@
       <c r="M89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N89">
+        <f>'2024 onward additions'!B16</f>
+        <v>0</v>
+      </c>
+      <c r="O89">
+        <f>'2024 onward additions'!C16</f>
+        <v>0</v>
+      </c>
+      <c r="P89">
+        <f>'2024 onward additions'!D16</f>
+        <v>0</v>
+      </c>
+      <c r="Q89">
+        <f>'2024 onward additions'!E16</f>
+        <v>0</v>
+      </c>
+      <c r="R89">
+        <f>'2024 onward additions'!F16</f>
+        <v>0</v>
+      </c>
+      <c r="S89">
+        <f>'2024 onward additions'!G16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>32</v>
       </c>
@@ -3754,8 +4150,32 @@
       <c r="M90">
         <v>0</v>
       </c>
-    </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N90">
+        <f>'2024 onward additions'!B17</f>
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <f>'2024 onward additions'!C17</f>
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <f>'2024 onward additions'!D17</f>
+        <v>0</v>
+      </c>
+      <c r="Q90">
+        <f>'2024 onward additions'!E17</f>
+        <v>0</v>
+      </c>
+      <c r="R90">
+        <f>'2024 onward additions'!F17</f>
+        <v>0</v>
+      </c>
+      <c r="S90">
+        <f>'2024 onward additions'!G17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>33</v>
       </c>
@@ -3795,8 +4215,32 @@
       <c r="M91">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N91">
+        <f>'2024 onward additions'!B18</f>
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <f>'2024 onward additions'!C18</f>
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <f>'2024 onward additions'!D18</f>
+        <v>0</v>
+      </c>
+      <c r="Q91">
+        <f>'2024 onward additions'!E18</f>
+        <v>0</v>
+      </c>
+      <c r="R91">
+        <f>'2024 onward additions'!F18</f>
+        <v>0</v>
+      </c>
+      <c r="S91">
+        <f>'2024 onward additions'!G18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>34</v>
       </c>
@@ -3836,8 +4280,32 @@
       <c r="M92">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N92">
+        <f>'2024 onward additions'!B19</f>
+        <v>0</v>
+      </c>
+      <c r="O92">
+        <f>'2024 onward additions'!C19</f>
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <f>'2024 onward additions'!D19</f>
+        <v>0</v>
+      </c>
+      <c r="Q92">
+        <f>'2024 onward additions'!E19</f>
+        <v>0</v>
+      </c>
+      <c r="R92">
+        <f>'2024 onward additions'!F19</f>
+        <v>0</v>
+      </c>
+      <c r="S92">
+        <f>'2024 onward additions'!G19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>35</v>
       </c>
@@ -3877,8 +4345,32 @@
       <c r="M93">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N93">
+        <f>'2024 onward additions'!B20</f>
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <f>'2024 onward additions'!C20</f>
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <f>'2024 onward additions'!D20</f>
+        <v>0</v>
+      </c>
+      <c r="Q93">
+        <f>'2024 onward additions'!E20</f>
+        <v>0</v>
+      </c>
+      <c r="R93">
+        <f>'2024 onward additions'!F20</f>
+        <v>0</v>
+      </c>
+      <c r="S93">
+        <f>'2024 onward additions'!G20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>36</v>
       </c>
@@ -3918,8 +4410,32 @@
       <c r="M94">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N94">
+        <f>'2024 onward additions'!B21</f>
+        <v>0</v>
+      </c>
+      <c r="O94">
+        <f>'2024 onward additions'!C21</f>
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <f>'2024 onward additions'!D21</f>
+        <v>0</v>
+      </c>
+      <c r="Q94">
+        <f>'2024 onward additions'!E21</f>
+        <v>0</v>
+      </c>
+      <c r="R94">
+        <f>'2024 onward additions'!F21</f>
+        <v>0</v>
+      </c>
+      <c r="S94">
+        <f>'2024 onward additions'!G21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>37</v>
       </c>
@@ -3959,8 +4475,32 @@
       <c r="M95">
         <v>0</v>
       </c>
-    </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N95">
+        <f>'2024 onward additions'!B22</f>
+        <v>0</v>
+      </c>
+      <c r="O95">
+        <f>'2024 onward additions'!C22</f>
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <f>'2024 onward additions'!D22</f>
+        <v>0</v>
+      </c>
+      <c r="Q95">
+        <f>'2024 onward additions'!E22</f>
+        <v>0</v>
+      </c>
+      <c r="R95">
+        <f>'2024 onward additions'!F22</f>
+        <v>0</v>
+      </c>
+      <c r="S95">
+        <f>'2024 onward additions'!G22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>38</v>
       </c>
@@ -4000,8 +4540,32 @@
       <c r="M96">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N96">
+        <f>'2024 onward additions'!B23</f>
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <f>'2024 onward additions'!C23</f>
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <f>'2024 onward additions'!D23</f>
+        <v>0</v>
+      </c>
+      <c r="Q96">
+        <f>'2024 onward additions'!E23</f>
+        <v>0</v>
+      </c>
+      <c r="R96">
+        <f>'2024 onward additions'!F23</f>
+        <v>0</v>
+      </c>
+      <c r="S96">
+        <f>'2024 onward additions'!G23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>39</v>
       </c>
@@ -4041,8 +4605,32 @@
       <c r="M97">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N97">
+        <f>'2024 onward additions'!B24</f>
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <f>'2024 onward additions'!C24</f>
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <f>'2024 onward additions'!D24</f>
+        <v>0</v>
+      </c>
+      <c r="Q97">
+        <f>'2024 onward additions'!E24</f>
+        <v>0</v>
+      </c>
+      <c r="R97">
+        <f>'2024 onward additions'!F24</f>
+        <v>0</v>
+      </c>
+      <c r="S97">
+        <f>'2024 onward additions'!G24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>40</v>
       </c>
@@ -4082,13 +4670,37 @@
       <c r="M98">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N98">
+        <f>'2024 onward additions'!B25</f>
+        <v>0</v>
+      </c>
+      <c r="O98">
+        <f>'2024 onward additions'!C25</f>
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <f>'2024 onward additions'!D25</f>
+        <v>0</v>
+      </c>
+      <c r="Q98">
+        <f>'2024 onward additions'!E25</f>
+        <v>0</v>
+      </c>
+      <c r="R98">
+        <f>'2024 onward additions'!F25</f>
+        <v>0</v>
+      </c>
+      <c r="S98">
+        <f>'2024 onward additions'!G25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>2012</v>
       </c>
@@ -4126,7 +4738,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>17</v>
       </c>
@@ -4167,7 +4779,7 @@
         <v>11.878174542582821</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -4208,7 +4820,7 @@
         <v>13.991493855527549</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>19</v>
       </c>
@@ -4249,7 +4861,7 @@
         <v>9.9125305465206051</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>20</v>
       </c>
@@ -4290,27 +4902,27 @@
         <v>14.588914368054644</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>25</v>
       </c>
@@ -4351,7 +4963,7 @@
         <v>28.466102501296842</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>26</v>
       </c>
@@ -5538,10 +6150,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDA73482-1B0D-4DBD-AEB7-A456FBA3A7C4}">
   <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="14" max="14" width="23.109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B1">
         <v>2024</v>
@@ -5562,13 +6177,13 @@
         <v>2029</v>
       </c>
       <c r="M1">
-        <v>18</v>
+        <v>1600</v>
       </c>
       <c r="N1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O1" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -5576,29 +6191,75 @@
         <v>17</v>
       </c>
       <c r="M2">
-        <v>100</v>
+        <f>448+930+400</f>
+        <v>1778</v>
       </c>
       <c r="N2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
+      <c r="M3">
+        <v>1436</v>
+      </c>
+      <c r="N3" t="s">
+        <v>88</v>
+      </c>
+      <c r="O3" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
+      <c r="B4">
+        <f>M2</f>
+        <v>1778</v>
+      </c>
+      <c r="C4">
+        <f>M3</f>
+        <v>1436</v>
+      </c>
+      <c r="D4">
+        <f>M4</f>
+        <v>1537</v>
+      </c>
+      <c r="E4">
+        <f>M5</f>
+        <v>1000</v>
+      </c>
+      <c r="M4">
+        <f>768+769</f>
+        <v>1537</v>
+      </c>
+      <c r="N4" t="s">
+        <v>85</v>
+      </c>
+      <c r="O4" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
+      <c r="M5">
+        <f>1000</f>
+        <v>1000</v>
+      </c>
+      <c r="N5" t="s">
+        <v>86</v>
+      </c>
+      <c r="O5" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -5613,7 +6274,7 @@
         <v>2471</v>
       </c>
       <c r="N7" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="O7" t="s">
         <v>74</v>
@@ -5624,8 +6285,8 @@
         <v>23</v>
       </c>
       <c r="B8">
-        <f>SUM(M1:M2)</f>
-        <v>118</v>
+        <f>M1</f>
+        <v>1600</v>
       </c>
       <c r="E8">
         <f>M7*0.19</f>
@@ -5643,7 +6304,7 @@
         <v>895</v>
       </c>
       <c r="N8" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
         <v>74</v>
@@ -5653,28 +6314,35 @@
       <c r="A9" t="s">
         <v>24</v>
       </c>
-      <c r="E9">
-        <f>M8*0.19</f>
-        <v>170.05</v>
-      </c>
-      <c r="F9">
-        <f>M8*0.78</f>
-        <v>698.1</v>
-      </c>
-      <c r="G9">
-        <f>M8*0.03</f>
-        <v>26.849999999999998</v>
-      </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>25</v>
       </c>
+      <c r="M10">
+        <v>360</v>
+      </c>
+      <c r="N10" t="s">
+        <v>90</v>
+      </c>
+      <c r="O10" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>26</v>
       </c>
+      <c r="M11">
+        <f>7620-7500</f>
+        <v>120</v>
+      </c>
+      <c r="N11" t="s">
+        <v>91</v>
+      </c>
+      <c r="O11" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -5694,6 +6362,26 @@
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
+      </c>
+      <c r="B15">
+        <f>M10</f>
+        <v>360</v>
+      </c>
+      <c r="C15">
+        <f>M11</f>
+        <v>120</v>
+      </c>
+      <c r="E15">
+        <f>M8*0.19</f>
+        <v>170.05</v>
+      </c>
+      <c r="F15">
+        <f>M8*0.78</f>
+        <v>698.1</v>
+      </c>
+      <c r="G15">
+        <f>M8*0.03</f>
+        <v>26.849999999999998</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -5758,6 +6446,9 @@
   </sheetPr>
   <dimension ref="A1:AZ25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="30.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -5937,24 +6628,31 @@
         <v>0</v>
       </c>
       <c r="F2">
+        <f>Data!N75</f>
         <v>0</v>
       </c>
       <c r="G2">
+        <f>Data!O75</f>
         <v>0</v>
       </c>
       <c r="H2">
+        <f>Data!P75</f>
         <v>0</v>
       </c>
       <c r="I2">
+        <f>Data!Q75</f>
         <v>0</v>
       </c>
       <c r="J2">
+        <f>Data!R75</f>
         <v>0</v>
       </c>
       <c r="K2">
+        <f>Data!S75</f>
         <v>0</v>
       </c>
       <c r="L2">
+        <f>Data!T75</f>
         <v>0</v>
       </c>
       <c r="M2">
@@ -6098,24 +6796,31 @@
         <v>4.5</v>
       </c>
       <c r="F3">
+        <f>Data!N76</f>
         <v>0</v>
       </c>
       <c r="G3">
+        <f>Data!O76</f>
         <v>0</v>
       </c>
       <c r="H3">
+        <f>Data!P76</f>
         <v>0</v>
       </c>
       <c r="I3">
+        <f>Data!Q76</f>
         <v>0</v>
       </c>
       <c r="J3">
+        <f>Data!R76</f>
         <v>0</v>
       </c>
       <c r="K3">
+        <f>Data!S76</f>
         <v>0</v>
       </c>
       <c r="L3">
+        <f>Data!T76</f>
         <v>0</v>
       </c>
       <c r="M3">
@@ -6259,24 +6964,31 @@
         <v>765</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <f>Data!N77</f>
+        <v>1778</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <f>Data!O77</f>
+        <v>1436</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <f>Data!P77</f>
+        <v>1537</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <f>Data!Q77</f>
+        <v>1000</v>
       </c>
       <c r="J4">
+        <f>Data!R77</f>
         <v>0</v>
       </c>
       <c r="K4">
+        <f>Data!S77</f>
         <v>0</v>
       </c>
       <c r="L4">
+        <f>Data!T77</f>
         <v>0</v>
       </c>
       <c r="M4">
@@ -6420,24 +7132,31 @@
         <v>0</v>
       </c>
       <c r="F5">
+        <f>Data!N78</f>
         <v>0</v>
       </c>
       <c r="G5">
+        <f>Data!O78</f>
         <v>0</v>
       </c>
       <c r="H5">
+        <f>Data!P78</f>
         <v>0</v>
       </c>
       <c r="I5">
+        <f>Data!Q78</f>
         <v>0</v>
       </c>
       <c r="J5">
+        <f>Data!R78</f>
         <v>0</v>
       </c>
       <c r="K5">
+        <f>Data!S78</f>
         <v>0</v>
       </c>
       <c r="L5">
+        <f>Data!T78</f>
         <v>0</v>
       </c>
       <c r="M5">
@@ -6581,24 +7300,31 @@
         <v>0</v>
       </c>
       <c r="F6">
+        <f>Data!N79</f>
         <v>0</v>
       </c>
       <c r="G6">
+        <f>Data!O79</f>
         <v>0</v>
       </c>
       <c r="H6">
+        <f>Data!P79</f>
         <v>0</v>
       </c>
       <c r="I6">
+        <f>Data!Q79</f>
         <v>0</v>
       </c>
       <c r="J6">
+        <f>Data!R79</f>
         <v>0</v>
       </c>
       <c r="K6">
+        <f>Data!S79</f>
         <v>0</v>
       </c>
       <c r="L6">
+        <f>Data!T79</f>
         <v>0</v>
       </c>
       <c r="M6">
@@ -6742,24 +7468,31 @@
         <v>134</v>
       </c>
       <c r="F7">
+        <f>Data!N80</f>
         <v>0</v>
       </c>
       <c r="G7">
+        <f>Data!O80</f>
         <v>0</v>
       </c>
       <c r="H7">
+        <f>Data!P80</f>
         <v>0</v>
       </c>
       <c r="I7">
+        <f>Data!Q80</f>
         <v>0</v>
       </c>
       <c r="J7">
+        <f>Data!R80</f>
         <v>0</v>
       </c>
       <c r="K7">
+        <f>Data!S80</f>
         <v>0</v>
       </c>
       <c r="L7">
+        <f>Data!T80</f>
         <v>0</v>
       </c>
       <c r="M7">
@@ -6903,24 +7636,31 @@
         <v>934</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <f>Data!N81</f>
+        <v>1600</v>
       </c>
       <c r="G8">
+        <f>Data!O81</f>
         <v>0</v>
       </c>
       <c r="H8">
+        <f>Data!P81</f>
         <v>0</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <f>Data!Q81</f>
+        <v>469.49</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <f>Data!R81</f>
+        <v>1927.38</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <f>Data!S81</f>
+        <v>74.13</v>
       </c>
       <c r="L8">
+        <f>Data!T81</f>
         <v>0</v>
       </c>
       <c r="M8">
@@ -7064,24 +7804,31 @@
         <v>0</v>
       </c>
       <c r="F9">
+        <f>Data!N82</f>
         <v>0</v>
       </c>
       <c r="G9">
+        <f>Data!O82</f>
         <v>0</v>
       </c>
       <c r="H9">
+        <f>Data!P82</f>
         <v>0</v>
       </c>
       <c r="I9">
+        <f>Data!Q82</f>
         <v>0</v>
       </c>
       <c r="J9">
+        <f>Data!R82</f>
         <v>0</v>
       </c>
       <c r="K9">
+        <f>Data!S82</f>
         <v>0</v>
       </c>
       <c r="L9">
+        <f>Data!T82</f>
         <v>0</v>
       </c>
       <c r="M9">
@@ -7225,24 +7972,31 @@
         <v>2.8779999999999291</v>
       </c>
       <c r="F10">
+        <f>Data!N83</f>
         <v>0</v>
       </c>
       <c r="G10">
+        <f>Data!O83</f>
         <v>0</v>
       </c>
       <c r="H10">
+        <f>Data!P83</f>
         <v>0</v>
       </c>
       <c r="I10">
+        <f>Data!Q83</f>
         <v>0</v>
       </c>
       <c r="J10">
+        <f>Data!R83</f>
         <v>0</v>
       </c>
       <c r="K10">
+        <f>Data!S83</f>
         <v>0</v>
       </c>
       <c r="L10">
+        <f>Data!T83</f>
         <v>0</v>
       </c>
       <c r="M10">
@@ -7386,24 +8140,31 @@
         <v>0</v>
       </c>
       <c r="F11">
+        <f>Data!N84</f>
         <v>0</v>
       </c>
       <c r="G11">
+        <f>Data!O84</f>
         <v>0</v>
       </c>
       <c r="H11">
+        <f>Data!P84</f>
         <v>0</v>
       </c>
       <c r="I11">
+        <f>Data!Q84</f>
         <v>0</v>
       </c>
       <c r="J11">
+        <f>Data!R84</f>
         <v>0</v>
       </c>
       <c r="K11">
+        <f>Data!S84</f>
         <v>0</v>
       </c>
       <c r="L11">
+        <f>Data!T84</f>
         <v>0</v>
       </c>
       <c r="M11">
@@ -7547,24 +8308,31 @@
         <v>0</v>
       </c>
       <c r="F12">
+        <f>Data!N85</f>
         <v>0</v>
       </c>
       <c r="G12">
+        <f>Data!O85</f>
         <v>0</v>
       </c>
       <c r="H12">
+        <f>Data!P85</f>
         <v>0</v>
       </c>
       <c r="I12">
+        <f>Data!Q85</f>
         <v>0</v>
       </c>
       <c r="J12">
+        <f>Data!R85</f>
         <v>0</v>
       </c>
       <c r="K12">
+        <f>Data!S85</f>
         <v>0</v>
       </c>
       <c r="L12">
+        <f>Data!T85</f>
         <v>0</v>
       </c>
       <c r="M12">
@@ -7708,24 +8476,31 @@
         <v>80</v>
       </c>
       <c r="F13">
+        <f>Data!N86</f>
         <v>0</v>
       </c>
       <c r="G13">
+        <f>Data!O86</f>
         <v>0</v>
       </c>
       <c r="H13">
+        <f>Data!P86</f>
         <v>0</v>
       </c>
       <c r="I13">
+        <f>Data!Q86</f>
         <v>0</v>
       </c>
       <c r="J13">
+        <f>Data!R86</f>
         <v>0</v>
       </c>
       <c r="K13">
+        <f>Data!S86</f>
         <v>0</v>
       </c>
       <c r="L13">
+        <f>Data!T86</f>
         <v>0</v>
       </c>
       <c r="M13">
@@ -7869,24 +8644,31 @@
         <v>0</v>
       </c>
       <c r="F14">
+        <f>Data!N87</f>
         <v>0</v>
       </c>
       <c r="G14">
+        <f>Data!O87</f>
         <v>0</v>
       </c>
       <c r="H14">
+        <f>Data!P87</f>
         <v>0</v>
       </c>
       <c r="I14">
+        <f>Data!Q87</f>
         <v>0</v>
       </c>
       <c r="J14">
+        <f>Data!R87</f>
         <v>0</v>
       </c>
       <c r="K14">
+        <f>Data!S87</f>
         <v>0</v>
       </c>
       <c r="L14">
+        <f>Data!T87</f>
         <v>0</v>
       </c>
       <c r="M14">
@@ -8030,24 +8812,31 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <f>Data!N88</f>
+        <v>360</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <f>Data!O88</f>
+        <v>120</v>
       </c>
       <c r="H15">
+        <f>Data!P88</f>
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <f>Data!Q88</f>
+        <v>170.05</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <f>Data!R88</f>
+        <v>698.1</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <f>Data!S88</f>
+        <v>26.849999999999998</v>
       </c>
       <c r="L15">
+        <f>Data!T88</f>
         <v>0</v>
       </c>
       <c r="M15">
@@ -8191,24 +8980,31 @@
         <v>0</v>
       </c>
       <c r="F16">
+        <f>Data!N89</f>
         <v>0</v>
       </c>
       <c r="G16">
+        <f>Data!O89</f>
         <v>0</v>
       </c>
       <c r="H16">
+        <f>Data!P89</f>
         <v>0</v>
       </c>
       <c r="I16">
+        <f>Data!Q89</f>
         <v>0</v>
       </c>
       <c r="J16">
+        <f>Data!R89</f>
         <v>0</v>
       </c>
       <c r="K16">
+        <f>Data!S89</f>
         <v>0</v>
       </c>
       <c r="L16">
+        <f>Data!T89</f>
         <v>0</v>
       </c>
       <c r="M16">
@@ -8352,24 +9148,31 @@
         <v>0</v>
       </c>
       <c r="F17">
+        <f>Data!N90</f>
         <v>0</v>
       </c>
       <c r="G17">
+        <f>Data!O90</f>
         <v>0</v>
       </c>
       <c r="H17">
+        <f>Data!P90</f>
         <v>0</v>
       </c>
       <c r="I17">
+        <f>Data!Q90</f>
         <v>0</v>
       </c>
       <c r="J17">
+        <f>Data!R90</f>
         <v>0</v>
       </c>
       <c r="K17">
+        <f>Data!S90</f>
         <v>0</v>
       </c>
       <c r="L17">
+        <f>Data!T90</f>
         <v>0</v>
       </c>
       <c r="M17">
@@ -8513,24 +9316,31 @@
         <v>0</v>
       </c>
       <c r="F18">
+        <f>Data!N91</f>
         <v>0</v>
       </c>
       <c r="G18">
+        <f>Data!O91</f>
         <v>0</v>
       </c>
       <c r="H18">
+        <f>Data!P91</f>
         <v>0</v>
       </c>
       <c r="I18">
+        <f>Data!Q91</f>
         <v>0</v>
       </c>
       <c r="J18">
+        <f>Data!R91</f>
         <v>0</v>
       </c>
       <c r="K18">
+        <f>Data!S91</f>
         <v>0</v>
       </c>
       <c r="L18">
+        <f>Data!T91</f>
         <v>0</v>
       </c>
       <c r="M18">
@@ -8674,24 +9484,31 @@
         <v>0</v>
       </c>
       <c r="F19">
+        <f>Data!N92</f>
         <v>0</v>
       </c>
       <c r="G19">
+        <f>Data!O92</f>
         <v>0</v>
       </c>
       <c r="H19">
+        <f>Data!P92</f>
         <v>0</v>
       </c>
       <c r="I19">
+        <f>Data!Q92</f>
         <v>0</v>
       </c>
       <c r="J19">
+        <f>Data!R92</f>
         <v>0</v>
       </c>
       <c r="K19">
+        <f>Data!S92</f>
         <v>0</v>
       </c>
       <c r="L19">
+        <f>Data!T92</f>
         <v>0</v>
       </c>
       <c r="M19">
@@ -8835,24 +9652,31 @@
         <v>0</v>
       </c>
       <c r="F20">
+        <f>Data!N93</f>
         <v>0</v>
       </c>
       <c r="G20">
+        <f>Data!O93</f>
         <v>0</v>
       </c>
       <c r="H20">
+        <f>Data!P93</f>
         <v>0</v>
       </c>
       <c r="I20">
+        <f>Data!Q93</f>
         <v>0</v>
       </c>
       <c r="J20">
+        <f>Data!R93</f>
         <v>0</v>
       </c>
       <c r="K20">
+        <f>Data!S93</f>
         <v>0</v>
       </c>
       <c r="L20">
+        <f>Data!T93</f>
         <v>0</v>
       </c>
       <c r="M20">
@@ -8996,24 +9820,31 @@
         <v>0</v>
       </c>
       <c r="F21">
+        <f>Data!N94</f>
         <v>0</v>
       </c>
       <c r="G21">
+        <f>Data!O94</f>
         <v>0</v>
       </c>
       <c r="H21">
+        <f>Data!P94</f>
         <v>0</v>
       </c>
       <c r="I21">
+        <f>Data!Q94</f>
         <v>0</v>
       </c>
       <c r="J21">
+        <f>Data!R94</f>
         <v>0</v>
       </c>
       <c r="K21">
+        <f>Data!S94</f>
         <v>0</v>
       </c>
       <c r="L21">
+        <f>Data!T94</f>
         <v>0</v>
       </c>
       <c r="M21">
@@ -9157,24 +9988,31 @@
         <v>0</v>
       </c>
       <c r="F22">
+        <f>Data!N95</f>
         <v>0</v>
       </c>
       <c r="G22">
+        <f>Data!O95</f>
         <v>0</v>
       </c>
       <c r="H22">
+        <f>Data!P95</f>
         <v>0</v>
       </c>
       <c r="I22">
+        <f>Data!Q95</f>
         <v>0</v>
       </c>
       <c r="J22">
+        <f>Data!R95</f>
         <v>0</v>
       </c>
       <c r="K22">
+        <f>Data!S95</f>
         <v>0</v>
       </c>
       <c r="L22">
+        <f>Data!T95</f>
         <v>0</v>
       </c>
       <c r="M22">
@@ -9318,24 +10156,31 @@
         <v>0</v>
       </c>
       <c r="F23">
+        <f>Data!N96</f>
         <v>0</v>
       </c>
       <c r="G23">
+        <f>Data!O96</f>
         <v>0</v>
       </c>
       <c r="H23">
+        <f>Data!P96</f>
         <v>0</v>
       </c>
       <c r="I23">
+        <f>Data!Q96</f>
         <v>0</v>
       </c>
       <c r="J23">
+        <f>Data!R96</f>
         <v>0</v>
       </c>
       <c r="K23">
+        <f>Data!S96</f>
         <v>0</v>
       </c>
       <c r="L23">
+        <f>Data!T96</f>
         <v>0</v>
       </c>
       <c r="M23">
@@ -9479,24 +10324,31 @@
         <v>0</v>
       </c>
       <c r="F24">
+        <f>Data!N97</f>
         <v>0</v>
       </c>
       <c r="G24">
+        <f>Data!O97</f>
         <v>0</v>
       </c>
       <c r="H24">
+        <f>Data!P97</f>
         <v>0</v>
       </c>
       <c r="I24">
+        <f>Data!Q97</f>
         <v>0</v>
       </c>
       <c r="J24">
+        <f>Data!R97</f>
         <v>0</v>
       </c>
       <c r="K24">
+        <f>Data!S97</f>
         <v>0</v>
       </c>
       <c r="L24">
+        <f>Data!T97</f>
         <v>0</v>
       </c>
       <c r="M24">
@@ -9640,24 +10492,31 @@
         <v>0</v>
       </c>
       <c r="F25">
+        <f>Data!N98</f>
         <v>0</v>
       </c>
       <c r="G25">
+        <f>Data!O98</f>
         <v>0</v>
       </c>
       <c r="H25">
+        <f>Data!P98</f>
         <v>0</v>
       </c>
       <c r="I25">
+        <f>Data!Q98</f>
         <v>0</v>
       </c>
       <c r="J25">
+        <f>Data!R98</f>
         <v>0</v>
       </c>
       <c r="K25">
+        <f>Data!S98</f>
         <v>0</v>
       </c>
       <c r="L25">
+        <f>Data!T98</f>
         <v>0</v>
       </c>
       <c r="M25">

--- a/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
+++ b/InputData/elec/BPMCCS/BAU Pol Mandated Cap Const Sched.xlsx
@@ -10643,4 +10643,211 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010027350D42B0D95040ACC873ED5DCB146E" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07e9ea90ad522b71e445466745b665d9">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="688c5d3b-a76a-458b-b159-91c2a1154680" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2528a4ec313a4f0a1f4e92f7a0496c8f" ns2:_="">
+    <xsd:import namespace="688c5d3b-a76a-458b-b159-91c2a1154680"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="688c5d3b-a76a-458b-b159-91c2a1154680" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="13" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="14" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="15" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="17" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="eca5b831-c3dc-41cf-bd85-218b82cecb21" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="688c5d3b-a76a-458b-b159-91c2a1154680">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{660F6349-2127-4B2A-B466-3F1557636D5A}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FD59CF7-F985-490C-822C-4DD575935105}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD994CBD-8BC0-4644-B472-665B068241BE}"/>
 </file>